--- a/informes_data/Primera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_HLA ALICANTE.xlsx
+++ b/informes_data/Primera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_HLA ALICANTE.xlsx
@@ -565,13 +565,13 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6719999999999999</v>
+        <v>-0.1343000000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>1.1381</v>
+        <v>0.4350999999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.4661999999999999</v>
+        <v>-0.5693999999999999</v>
       </c>
       <c r="G2" t="n">
         <v>-1.2073</v>
@@ -610,13 +610,13 @@
         <v>0.2203</v>
       </c>
       <c r="S2" t="n">
-        <v>0.8722000000000001</v>
+        <v>0.066</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6294</v>
+        <v>-0.07350000000000001</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2427</v>
+        <v>0.1395</v>
       </c>
       <c r="V2" t="n">
         <v>1.007</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>B. COULIBALY</t>
+          <t>Y. JOSEPH</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>-2.1845</v>
+        <v>-1.4095</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2914999999999999</v>
+        <v>4.8393</v>
       </c>
       <c r="F3" t="n">
-        <v>-2.4761</v>
+        <v>-6.2488</v>
       </c>
       <c r="G3" t="n">
-        <v>-1.0099</v>
+        <v>3.8984</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.2697000000000001</v>
+        <v>1.2566</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.7402</v>
+        <v>2.6418</v>
       </c>
       <c r="J3" t="n">
-        <v>0.7248999999999999</v>
+        <v>10.5064</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.03450000000000009</v>
+        <v>1.9619</v>
       </c>
       <c r="L3" t="n">
-        <v>0.7594</v>
+        <v>8.5444</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.7348</v>
+        <v>-6.6079</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.2350999999999999</v>
+        <v>-0.7053999999999999</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.4996</v>
+        <v>-5.9027</v>
       </c>
       <c r="P3" t="n">
-        <v>-1.1014</v>
+        <v>-2.6432</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.2027</v>
+        <v>-5.7271</v>
       </c>
       <c r="R3" t="n">
-        <v>1.1013</v>
+        <v>3.0838</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7081000000000001</v>
+        <v>-1.0612</v>
       </c>
       <c r="T3" t="n">
-        <v>0.4654</v>
+        <v>-1.2439</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2428</v>
+        <v>0.1826</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.7813999999999999</v>
+        <v>-1.6034</v>
       </c>
       <c r="W3" t="n">
         <v>1.3039</v>
       </c>
       <c r="X3" t="n">
-        <v>-2.0853</v>
+        <v>-2.9073</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>K. LARSEN</t>
+          <t>B. COULIBALY</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>-2.322700000000001</v>
+        <v>-2.1556</v>
       </c>
       <c r="E4" t="n">
-        <v>3.346</v>
+        <v>-0.1771</v>
       </c>
       <c r="F4" t="n">
-        <v>-5.6687</v>
+        <v>-1.9785</v>
       </c>
       <c r="G4" t="n">
-        <v>-3.3014</v>
+        <v>-1.0099</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.3621000000000003</v>
+        <v>-0.2697000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>-2.9393</v>
+        <v>-0.7402</v>
       </c>
       <c r="J4" t="n">
-        <v>5.5038</v>
+        <v>0.7248999999999999</v>
       </c>
       <c r="K4" t="n">
-        <v>1.6248</v>
+        <v>-0.03450000000000009</v>
       </c>
       <c r="L4" t="n">
-        <v>3.8789</v>
+        <v>0.7594</v>
       </c>
       <c r="M4" t="n">
-        <v>-8.805199999999999</v>
+        <v>-1.7348</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.9869</v>
+        <v>-0.2350999999999999</v>
       </c>
       <c r="O4" t="n">
-        <v>-6.8183</v>
+        <v>-1.4996</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.9825</v>
+        <v>-1.1014</v>
       </c>
       <c r="Q4" t="n">
-        <v>-5.7271</v>
+        <v>-2.2027</v>
       </c>
       <c r="R4" t="n">
-        <v>3.7447</v>
+        <v>1.1013</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7277999999999998</v>
+        <v>0.7369</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.3424</v>
+        <v>-0.003199999999999981</v>
       </c>
       <c r="U4" t="n">
-        <v>1.0703</v>
+        <v>0.7402</v>
       </c>
       <c r="V4" t="n">
-        <v>2.2334</v>
+        <v>-0.7813999999999999</v>
       </c>
       <c r="W4" t="n">
-        <v>3.9117</v>
+        <v>1.3039</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.6784</v>
+        <v>-2.0853</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Y. JOSEPH</t>
+          <t>S. LLORENTE PAZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>-2.8368</v>
+        <v>-3.6196</v>
       </c>
       <c r="E5" t="n">
-        <v>4.3706</v>
+        <v>0.325</v>
       </c>
       <c r="F5" t="n">
-        <v>-7.2074</v>
+        <v>-3.9447</v>
       </c>
       <c r="G5" t="n">
-        <v>3.8984</v>
+        <v>-0.785</v>
       </c>
       <c r="H5" t="n">
-        <v>1.2566</v>
+        <v>-1.1061</v>
       </c>
       <c r="I5" t="n">
-        <v>2.6418</v>
+        <v>0.3210000000000002</v>
       </c>
       <c r="J5" t="n">
-        <v>10.5064</v>
+        <v>3.2563</v>
       </c>
       <c r="K5" t="n">
-        <v>1.9619</v>
+        <v>0.2073</v>
       </c>
       <c r="L5" t="n">
-        <v>8.5444</v>
+        <v>3.0488</v>
       </c>
       <c r="M5" t="n">
-        <v>-6.6079</v>
+        <v>-4.0413</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.7053999999999999</v>
+        <v>-1.3135</v>
       </c>
       <c r="O5" t="n">
-        <v>-5.9027</v>
+        <v>-2.7278</v>
       </c>
       <c r="P5" t="n">
-        <v>-2.6432</v>
+        <v>-4.1852</v>
       </c>
       <c r="Q5" t="n">
         <v>-5.7271</v>
       </c>
       <c r="R5" t="n">
-        <v>3.0838</v>
+        <v>1.5419</v>
       </c>
       <c r="S5" t="n">
-        <v>-2.4885</v>
+        <v>-0.4055</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.7124</v>
+        <v>-0.5610000000000001</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.776</v>
+        <v>0.1556</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.6034</v>
+        <v>1.756</v>
       </c>
       <c r="W5" t="n">
-        <v>1.3039</v>
+        <v>3.3568</v>
       </c>
       <c r="X5" t="n">
-        <v>-2.9073</v>
+        <v>-1.6008</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S. LLORENTE PAZ</t>
+          <t>K. LARSEN</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>-3.6651</v>
+        <v>-3.863599999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3781</v>
+        <v>2.4727</v>
       </c>
       <c r="F6" t="n">
-        <v>-4.0432</v>
+        <v>-6.3363</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.785</v>
+        <v>-3.3014</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.1061</v>
+        <v>-0.3621000000000003</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3210000000000002</v>
+        <v>-2.9393</v>
       </c>
       <c r="J6" t="n">
-        <v>3.2563</v>
+        <v>5.5038</v>
       </c>
       <c r="K6" t="n">
-        <v>0.2073</v>
+        <v>1.6248</v>
       </c>
       <c r="L6" t="n">
-        <v>3.0488</v>
+        <v>3.8789</v>
       </c>
       <c r="M6" t="n">
-        <v>-4.0413</v>
+        <v>-8.805199999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.3135</v>
+        <v>-1.9869</v>
       </c>
       <c r="O6" t="n">
-        <v>-2.7278</v>
+        <v>-6.8183</v>
       </c>
       <c r="P6" t="n">
-        <v>-4.1852</v>
+        <v>-1.9825</v>
       </c>
       <c r="Q6" t="n">
         <v>-5.7271</v>
       </c>
       <c r="R6" t="n">
-        <v>1.5419</v>
+        <v>3.7447</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.4509</v>
+        <v>-0.8129999999999999</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.5078</v>
+        <v>-1.2158</v>
       </c>
       <c r="U6" t="n">
-        <v>0.05699999999999994</v>
+        <v>0.4026</v>
       </c>
       <c r="V6" t="n">
-        <v>1.756</v>
+        <v>2.2334</v>
       </c>
       <c r="W6" t="n">
-        <v>3.3568</v>
+        <v>3.9117</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.6008</v>
+        <v>-1.6784</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>U. MENDICOTE RUBIO</t>
+          <t>E. POLANCO TAVAREZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>-4.7475</v>
+        <v>-4.4392</v>
       </c>
       <c r="E7" t="n">
-        <v>1.1953</v>
+        <v>-1.7559</v>
       </c>
       <c r="F7" t="n">
-        <v>-5.9428</v>
+        <v>-2.6832</v>
       </c>
       <c r="G7" t="n">
-        <v>-3.3296</v>
+        <v>-4.693000000000001</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.5686</v>
+        <v>-4.334000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.7609000000000001</v>
+        <v>-0.359</v>
       </c>
       <c r="J7" t="n">
-        <v>2.7939</v>
+        <v>1.3766</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.716</v>
+        <v>-2.5351</v>
       </c>
       <c r="L7" t="n">
-        <v>3.5098</v>
+        <v>3.9117</v>
       </c>
       <c r="M7" t="n">
-        <v>-6.1233</v>
+        <v>-6.0696</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.8527</v>
+        <v>-1.7988</v>
       </c>
       <c r="O7" t="n">
         <v>-4.2708</v>
       </c>
       <c r="P7" t="n">
-        <v>0.2202999999999999</v>
+        <v>-1.1014</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.1014</v>
+        <v>-3.5244</v>
       </c>
       <c r="R7" t="n">
-        <v>1.3216</v>
+        <v>2.423</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2153</v>
+        <v>0.1632</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3033</v>
+        <v>-1.0969</v>
       </c>
       <c r="U7" t="n">
-        <v>0.08810000000000001</v>
+        <v>1.2602</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.4229</v>
+        <v>1.192</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.1939</v>
+        <v>1.4889</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.229</v>
+        <v>-0.2969</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>E. POLANCO TAVAREZ</t>
+          <t>U. MENDICOTE RUBIO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>-5.25</v>
+        <v>-4.7885</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.576</v>
+        <v>0.7266</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.6739</v>
+        <v>-5.5151</v>
       </c>
       <c r="G8" t="n">
-        <v>-4.693000000000001</v>
+        <v>-3.3296</v>
       </c>
       <c r="H8" t="n">
-        <v>-4.334000000000001</v>
+        <v>-2.5686</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.359</v>
+        <v>-0.7609000000000001</v>
       </c>
       <c r="J8" t="n">
-        <v>1.3766</v>
+        <v>2.7939</v>
       </c>
       <c r="K8" t="n">
-        <v>-2.5351</v>
+        <v>-0.716</v>
       </c>
       <c r="L8" t="n">
-        <v>3.9117</v>
+        <v>3.5098</v>
       </c>
       <c r="M8" t="n">
-        <v>-6.0696</v>
+        <v>-6.1233</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.7988</v>
+        <v>-1.8527</v>
       </c>
       <c r="O8" t="n">
         <v>-4.2708</v>
       </c>
       <c r="P8" t="n">
+        <v>0.2202999999999999</v>
+      </c>
+      <c r="Q8" t="n">
         <v>-1.1014</v>
       </c>
-      <c r="Q8" t="n">
-        <v>-3.5244</v>
-      </c>
       <c r="R8" t="n">
-        <v>2.423</v>
+        <v>1.3216</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.6476</v>
+        <v>-0.2562</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.9171</v>
+        <v>-0.772</v>
       </c>
       <c r="U8" t="n">
-        <v>1.2695</v>
+        <v>0.5157999999999999</v>
       </c>
       <c r="V8" t="n">
-        <v>1.192</v>
+        <v>-1.4229</v>
       </c>
       <c r="W8" t="n">
-        <v>1.4889</v>
+        <v>-0.1939</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.2969</v>
+        <v>-1.229</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>-5.4573</v>
+        <v>-5.2035</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.0926</v>
+        <v>-1.4973</v>
       </c>
       <c r="F9" t="n">
-        <v>-4.3646</v>
+        <v>-3.7063</v>
       </c>
       <c r="G9" t="n">
         <v>-4.4691</v>
@@ -1156,13 +1156,13 @@
         <v>2.4229</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.1427</v>
+        <v>-0.889</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6517000000000001</v>
+        <v>-1.0562</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.4911</v>
+        <v>0.1673</v>
       </c>
       <c r="V9" t="n">
         <v>-2.0483</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. MWEMA</t>
+          <t>S. HOLLANDERS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>-7.2252</v>
+        <v>-5.3352</v>
       </c>
       <c r="E10" t="n">
-        <v>-6.6005</v>
+        <v>-1.5844</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.6247</v>
+        <v>-3.7508</v>
       </c>
       <c r="G10" t="n">
-        <v>-6.1567</v>
+        <v>-6.8331</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.6259</v>
+        <v>-1.7144</v>
       </c>
       <c r="I10" t="n">
-        <v>-4.5308</v>
+        <v>-5.1187</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.537</v>
+        <v>0.5109000000000004</v>
       </c>
       <c r="K10" t="n">
-        <v>0.3594000000000001</v>
+        <v>-1.345</v>
       </c>
       <c r="L10" t="n">
-        <v>-2.8965</v>
+        <v>1.8559</v>
       </c>
       <c r="M10" t="n">
-        <v>-3.6197</v>
+        <v>-7.3439</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.9854</v>
+        <v>-0.3693</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.6343</v>
+        <v>-6.9745</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.2203</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.423</v>
+        <v>-3.5243</v>
       </c>
       <c r="R10" t="n">
-        <v>2.2027</v>
+        <v>3.5244</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2844</v>
+        <v>-1.3744</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.0765</v>
+        <v>-1.5532</v>
       </c>
       <c r="U10" t="n">
-        <v>0.7922</v>
+        <v>0.1787</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.5639</v>
+        <v>2.8722</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.5639</v>
+        <v>2.9823</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-0.1101</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>S. HOLLANDERS</t>
+          <t>J. MWEMA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>-7.4664</v>
+        <v>-6.9518</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.4687</v>
+        <v>-6.4834</v>
       </c>
       <c r="F11" t="n">
-        <v>-4.997800000000001</v>
+        <v>-0.4684999999999999</v>
       </c>
       <c r="G11" t="n">
-        <v>-6.8331</v>
+        <v>-6.1567</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.7144</v>
+        <v>-1.6259</v>
       </c>
       <c r="I11" t="n">
-        <v>-5.1187</v>
+        <v>-4.5308</v>
       </c>
       <c r="J11" t="n">
-        <v>0.5109000000000004</v>
+        <v>-2.537</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.345</v>
+        <v>0.3594000000000001</v>
       </c>
       <c r="L11" t="n">
-        <v>1.8559</v>
+        <v>-2.8965</v>
       </c>
       <c r="M11" t="n">
-        <v>-7.3439</v>
+        <v>-3.6197</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.3693</v>
+        <v>-1.9854</v>
       </c>
       <c r="O11" t="n">
-        <v>-6.9745</v>
+        <v>-1.6343</v>
       </c>
       <c r="P11" t="n">
+        <v>-0.2203</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>-2.423</v>
+      </c>
+      <c r="R11" t="n">
+        <v>2.2027</v>
+      </c>
+      <c r="S11" t="n">
+        <v>-0.01099999999999998</v>
+      </c>
+      <c r="T11" t="n">
+        <v>-0.9593</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0.9483999999999999</v>
+      </c>
+      <c r="V11" t="n">
+        <v>-0.5639</v>
+      </c>
+      <c r="W11" t="n">
+        <v>-0.5639</v>
+      </c>
+      <c r="X11" t="n">
         <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>-3.5243</v>
-      </c>
-      <c r="R11" t="n">
-        <v>3.5244</v>
-      </c>
-      <c r="S11" t="n">
-        <v>-3.5055</v>
-      </c>
-      <c r="T11" t="n">
-        <v>-2.4374</v>
-      </c>
-      <c r="U11" t="n">
-        <v>-1.0681</v>
-      </c>
-      <c r="V11" t="n">
-        <v>2.8722</v>
-      </c>
-      <c r="W11" t="n">
-        <v>2.9823</v>
-      </c>
-      <c r="X11" t="n">
-        <v>-0.1101</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>-8.723000000000001</v>
+        <v>-8.1309</v>
       </c>
       <c r="E12" t="n">
-        <v>-6.2774</v>
+        <v>-5.6276</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.4456</v>
+        <v>-2.5032</v>
       </c>
       <c r="G12" t="n">
         <v>-2.7275</v>
@@ -1390,13 +1390,13 @@
         <v>1.9824</v>
       </c>
       <c r="S12" t="n">
-        <v>-2.2334</v>
+        <v>-1.6411</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.6654</v>
+        <v>-1.0156</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.5679000000000001</v>
+        <v>-0.6256</v>
       </c>
       <c r="V12" t="n">
         <v>-1.1189</v>
@@ -1423,13 +1423,13 @@
         <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>-12.9603</v>
+        <v>-11.9095</v>
       </c>
       <c r="E13" t="n">
-        <v>-10.1574</v>
+        <v>-9.805900000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.8028</v>
+        <v>-2.1036</v>
       </c>
       <c r="G13" t="n">
         <v>-8.744</v>
@@ -1468,13 +1468,13 @@
         <v>1.7622</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.8928</v>
+        <v>-0.842</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.1609</v>
+        <v>-0.8093999999999999</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.7319</v>
+        <v>-0.03270000000000001</v>
       </c>
       <c r="V13" t="n">
         <v>1.6413</v>
@@ -1501,13 +1501,13 @@
         <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>-62.16679999999999</v>
+        <v>-57.9412</v>
       </c>
       <c r="E14" t="n">
-        <v>-18.453</v>
+        <v>-18.1329</v>
       </c>
       <c r="F14" t="n">
-        <v>-43.71379999999999</v>
+        <v>-39.8084</v>
       </c>
       <c r="G14" t="n">
         <v>-39.3582</v>
@@ -1522,7 +1522,7 @@
         <v>16.0315</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.6483000000000011</v>
+        <v>-0.6483000000000002</v>
       </c>
       <c r="L14" t="n">
         <v>16.67899999999999</v>
@@ -1546,13 +1546,13 @@
         <v>25.3312</v>
       </c>
       <c r="S14" t="n">
-        <v>-10.553</v>
+        <v>-6.3273</v>
       </c>
       <c r="T14" t="n">
-        <v>-10.6801</v>
+        <v>-10.36</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1275999999999997</v>
+        <v>4.0326</v>
       </c>
       <c r="V14" t="n">
         <v>3.1631</v>
